--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260825.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260825.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>13,112,000</t>
+          <t>2,580,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,580,000</t>
+          <t>13,112,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>28,657,000</t>
+          <t>2,330,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2,330,000</t>
+          <t>8,422,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>8,422,000</t>
+          <t>28,657,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
